--- a/server/CRM/CRM/wwwroot/UploadFiles/ThongTinKhachHang (2).xlsx
+++ b/server/CRM/CRM/wwwroot/UploadFiles/ThongTinKhachHang (2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSIs\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D68FDA0-E26C-4692-AF0A-0B4EF0F02906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46ABED86-F170-4C2C-9C15-E436D3368851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1752" yWindow="576" windowWidth="21120" windowHeight="10512" xr2:uid="{97B07EE4-0850-4CD7-A078-E42B6BC90780}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{97B07EE4-0850-4CD7-A078-E42B6BC90780}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="203">
   <si>
     <t>Tên Khách Hàng</t>
   </si>
@@ -81,19 +81,559 @@
     <t>Khách hàng cá nhân</t>
   </si>
   <si>
-    <t>Khách hàng 4</t>
-  </si>
-  <si>
-    <t>text@1123</t>
+    <t>Khách hàng 10</t>
+  </si>
+  <si>
+    <t>test@345</t>
   </si>
   <si>
     <t>Nhân viên kinh doanh tự tìm kiếm</t>
   </si>
   <si>
-    <t>Khách hàng bán lẻ</t>
-  </si>
-  <si>
-    <t>ưqeqxq</t>
+    <t>Khách hàng 11</t>
+  </si>
+  <si>
+    <t>Khách hàng 12</t>
+  </si>
+  <si>
+    <t>Khách hàng 13</t>
+  </si>
+  <si>
+    <t>Khách hàng 14</t>
+  </si>
+  <si>
+    <t>Khách hàng 15</t>
+  </si>
+  <si>
+    <t>Khách hàng 16</t>
+  </si>
+  <si>
+    <t>Khách hàng 17</t>
+  </si>
+  <si>
+    <t>Khách hàng 18</t>
+  </si>
+  <si>
+    <t>Khách hàng 19</t>
+  </si>
+  <si>
+    <t>Khách hàng 20</t>
+  </si>
+  <si>
+    <t>Khách hàng 21</t>
+  </si>
+  <si>
+    <t>Khách hàng 22</t>
+  </si>
+  <si>
+    <t>Khách hàng 23</t>
+  </si>
+  <si>
+    <t>Khách hàng 24</t>
+  </si>
+  <si>
+    <t>Khách hàng 25</t>
+  </si>
+  <si>
+    <t>Khách hàng 26</t>
+  </si>
+  <si>
+    <t>Khách hàng 27</t>
+  </si>
+  <si>
+    <t>Khách hàng 28</t>
+  </si>
+  <si>
+    <t>Khách hàng 29</t>
+  </si>
+  <si>
+    <t>Khách hàng 30</t>
+  </si>
+  <si>
+    <t>Khách hàng 31</t>
+  </si>
+  <si>
+    <t>Khách hàng 32</t>
+  </si>
+  <si>
+    <t>Khách hàng 33</t>
+  </si>
+  <si>
+    <t>Khách hàng 34</t>
+  </si>
+  <si>
+    <t>Khách hàng 35</t>
+  </si>
+  <si>
+    <t>Khách hàng 36</t>
+  </si>
+  <si>
+    <t>Khách hàng 37</t>
+  </si>
+  <si>
+    <t>Khách hàng 38</t>
+  </si>
+  <si>
+    <t>Khách hàng 39</t>
+  </si>
+  <si>
+    <t>Khách hàng 40</t>
+  </si>
+  <si>
+    <t>Khách hàng 41</t>
+  </si>
+  <si>
+    <t>Khách hàng 42</t>
+  </si>
+  <si>
+    <t>Khách hàng 43</t>
+  </si>
+  <si>
+    <t>Khách hàng 44</t>
+  </si>
+  <si>
+    <t>Khách hàng 45</t>
+  </si>
+  <si>
+    <t>Khách hàng 46</t>
+  </si>
+  <si>
+    <t>Khách hàng 47</t>
+  </si>
+  <si>
+    <t>Khách hàng 48</t>
+  </si>
+  <si>
+    <t>Khách hàng 49</t>
+  </si>
+  <si>
+    <t>Khách hàng 50</t>
+  </si>
+  <si>
+    <t>Khách hàng 51</t>
+  </si>
+  <si>
+    <t>Khách hàng 52</t>
+  </si>
+  <si>
+    <t>Khách hàng 53</t>
+  </si>
+  <si>
+    <t>Khách hàng 54</t>
+  </si>
+  <si>
+    <t>Khách hàng 55</t>
+  </si>
+  <si>
+    <t>Khách hàng 56</t>
+  </si>
+  <si>
+    <t>Khách hàng 57</t>
+  </si>
+  <si>
+    <t>Khách hàng 58</t>
+  </si>
+  <si>
+    <t>Khách hàng 59</t>
+  </si>
+  <si>
+    <t>Khách hàng 60</t>
+  </si>
+  <si>
+    <t>Khách hàng 61</t>
+  </si>
+  <si>
+    <t>Khách hàng 62</t>
+  </si>
+  <si>
+    <t>Khách hàng 63</t>
+  </si>
+  <si>
+    <t>Khách hàng 64</t>
+  </si>
+  <si>
+    <t>Khách hàng 65</t>
+  </si>
+  <si>
+    <t>Khách hàng 66</t>
+  </si>
+  <si>
+    <t>Khách hàng 67</t>
+  </si>
+  <si>
+    <t>Khách hàng 68</t>
+  </si>
+  <si>
+    <t>Khách hàng 69</t>
+  </si>
+  <si>
+    <t>Khách hàng 70</t>
+  </si>
+  <si>
+    <t>Khách hàng 71</t>
+  </si>
+  <si>
+    <t>Khách hàng 72</t>
+  </si>
+  <si>
+    <t>Khách hàng 73</t>
+  </si>
+  <si>
+    <t>Khách hàng 74</t>
+  </si>
+  <si>
+    <t>Khách hàng 75</t>
+  </si>
+  <si>
+    <t>Khách hàng 76</t>
+  </si>
+  <si>
+    <t>Khách hàng 77</t>
+  </si>
+  <si>
+    <t>Khách hàng 78</t>
+  </si>
+  <si>
+    <t>Khách hàng 79</t>
+  </si>
+  <si>
+    <t>Khách hàng 80</t>
+  </si>
+  <si>
+    <t>Khách hàng 81</t>
+  </si>
+  <si>
+    <t>Khách hàng 82</t>
+  </si>
+  <si>
+    <t>Khách hàng 83</t>
+  </si>
+  <si>
+    <t>Khách hàng 84</t>
+  </si>
+  <si>
+    <t>Khách hàng 85</t>
+  </si>
+  <si>
+    <t>Khách hàng 86</t>
+  </si>
+  <si>
+    <t>Khách hàng 87</t>
+  </si>
+  <si>
+    <t>Khách hàng 88</t>
+  </si>
+  <si>
+    <t>Khách hàng 89</t>
+  </si>
+  <si>
+    <t>Khách hàng 90</t>
+  </si>
+  <si>
+    <t>Khách hàng 91</t>
+  </si>
+  <si>
+    <t>Khách hàng 92</t>
+  </si>
+  <si>
+    <t>Khách hàng 93</t>
+  </si>
+  <si>
+    <t>Khách hàng 94</t>
+  </si>
+  <si>
+    <t>Khách hàng 95</t>
+  </si>
+  <si>
+    <t>Khách hàng 96</t>
+  </si>
+  <si>
+    <t>Khách hàng 97</t>
+  </si>
+  <si>
+    <t>Khách hàng 98</t>
+  </si>
+  <si>
+    <t>Khách hàng 99</t>
+  </si>
+  <si>
+    <t>Khách hàng 100</t>
+  </si>
+  <si>
+    <t>Khách hàng 101</t>
+  </si>
+  <si>
+    <t>Khách hàng 102</t>
+  </si>
+  <si>
+    <t>Khách hàng 103</t>
+  </si>
+  <si>
+    <t>Khách hàng 104</t>
+  </si>
+  <si>
+    <t>Khách hàng 105</t>
+  </si>
+  <si>
+    <t>Khách hàng 106</t>
+  </si>
+  <si>
+    <t>Khách hàng 107</t>
+  </si>
+  <si>
+    <t>Khách hàng 108</t>
+  </si>
+  <si>
+    <t>test@346</t>
+  </si>
+  <si>
+    <t>test@347</t>
+  </si>
+  <si>
+    <t>test@348</t>
+  </si>
+  <si>
+    <t>test@349</t>
+  </si>
+  <si>
+    <t>test@350</t>
+  </si>
+  <si>
+    <t>test@351</t>
+  </si>
+  <si>
+    <t>test@352</t>
+  </si>
+  <si>
+    <t>test@353</t>
+  </si>
+  <si>
+    <t>test@354</t>
+  </si>
+  <si>
+    <t>test@355</t>
+  </si>
+  <si>
+    <t>test@356</t>
+  </si>
+  <si>
+    <t>test@357</t>
+  </si>
+  <si>
+    <t>test@358</t>
+  </si>
+  <si>
+    <t>test@359</t>
+  </si>
+  <si>
+    <t>test@360</t>
+  </si>
+  <si>
+    <t>test@361</t>
+  </si>
+  <si>
+    <t>test@362</t>
+  </si>
+  <si>
+    <t>test@363</t>
+  </si>
+  <si>
+    <t>test@364</t>
+  </si>
+  <si>
+    <t>test@365</t>
+  </si>
+  <si>
+    <t>test@366</t>
+  </si>
+  <si>
+    <t>test@367</t>
+  </si>
+  <si>
+    <t>test@368</t>
+  </si>
+  <si>
+    <t>test@369</t>
+  </si>
+  <si>
+    <t>test@370</t>
+  </si>
+  <si>
+    <t>test@371</t>
+  </si>
+  <si>
+    <t>test@372</t>
+  </si>
+  <si>
+    <t>test@373</t>
+  </si>
+  <si>
+    <t>test@374</t>
+  </si>
+  <si>
+    <t>test@375</t>
+  </si>
+  <si>
+    <t>test@376</t>
+  </si>
+  <si>
+    <t>test@377</t>
+  </si>
+  <si>
+    <t>test@378</t>
+  </si>
+  <si>
+    <t>test@379</t>
+  </si>
+  <si>
+    <t>test@380</t>
+  </si>
+  <si>
+    <t>test@381</t>
+  </si>
+  <si>
+    <t>test@382</t>
+  </si>
+  <si>
+    <t>test@383</t>
+  </si>
+  <si>
+    <t>test@384</t>
+  </si>
+  <si>
+    <t>test@385</t>
+  </si>
+  <si>
+    <t>test@386</t>
+  </si>
+  <si>
+    <t>test@387</t>
+  </si>
+  <si>
+    <t>test@388</t>
+  </si>
+  <si>
+    <t>test@389</t>
+  </si>
+  <si>
+    <t>test@390</t>
+  </si>
+  <si>
+    <t>test@391</t>
+  </si>
+  <si>
+    <t>test@392</t>
+  </si>
+  <si>
+    <t>test@393</t>
+  </si>
+  <si>
+    <t>test@394</t>
+  </si>
+  <si>
+    <t>test@395</t>
+  </si>
+  <si>
+    <t>test@396</t>
+  </si>
+  <si>
+    <t>test@397</t>
+  </si>
+  <si>
+    <t>test@398</t>
+  </si>
+  <si>
+    <t>test@399</t>
+  </si>
+  <si>
+    <t>test@400</t>
+  </si>
+  <si>
+    <t>test@401</t>
+  </si>
+  <si>
+    <t>test@402</t>
+  </si>
+  <si>
+    <t>test@403</t>
+  </si>
+  <si>
+    <t>test@404</t>
+  </si>
+  <si>
+    <t>test@405</t>
+  </si>
+  <si>
+    <t>test@406</t>
+  </si>
+  <si>
+    <t>test@407</t>
+  </si>
+  <si>
+    <t>test@408</t>
+  </si>
+  <si>
+    <t>test@409</t>
+  </si>
+  <si>
+    <t>test@410</t>
+  </si>
+  <si>
+    <t>test@411</t>
+  </si>
+  <si>
+    <t>test@412</t>
+  </si>
+  <si>
+    <t>test@413</t>
+  </si>
+  <si>
+    <t>test@414</t>
+  </si>
+  <si>
+    <t>test@415</t>
+  </si>
+  <si>
+    <t>test@416</t>
+  </si>
+  <si>
+    <t>test@417</t>
+  </si>
+  <si>
+    <t>test@418</t>
+  </si>
+  <si>
+    <t>test@419</t>
+  </si>
+  <si>
+    <t>test@420</t>
+  </si>
+  <si>
+    <t>test@421</t>
+  </si>
+  <si>
+    <t>test@422</t>
+  </si>
+  <si>
+    <t>test@423</t>
+  </si>
+  <si>
+    <t>test@424</t>
+  </si>
+  <si>
+    <t>test@425</t>
+  </si>
+  <si>
+    <t>test@426</t>
+  </si>
+  <si>
+    <t>test@427</t>
+  </si>
+  <si>
+    <t>test@428</t>
+  </si>
+  <si>
+    <t>test@429</t>
   </si>
 </sst>
 </file>
@@ -104,7 +644,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +669,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -560,7 +1106,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="2">
-        <v>930910391</v>
+        <v>391230913</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>19</v>
@@ -568,343 +1114,1287 @@
       <c r="F2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="K2" s="4">
+        <v>37327</v>
+      </c>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="2" t="s">
+      <c r="D3" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K11" s="4"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K17" s="4"/>
-    </row>
-    <row r="18" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K18" s="4"/>
-    </row>
-    <row r="19" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K19" s="4"/>
-    </row>
-    <row r="20" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K20" s="4"/>
-    </row>
-    <row r="21" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K21" s="4"/>
-    </row>
-    <row r="22" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K22" s="4"/>
-    </row>
-    <row r="23" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K23" s="4"/>
-    </row>
-    <row r="24" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K24" s="4"/>
-    </row>
-    <row r="25" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K25" s="4"/>
-    </row>
-    <row r="26" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K26" s="4"/>
-    </row>
-    <row r="27" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K27" s="4"/>
-    </row>
-    <row r="28" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K28" s="4"/>
-    </row>
-    <row r="29" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K29" s="4"/>
-    </row>
-    <row r="30" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K30" s="4"/>
-    </row>
-    <row r="31" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K31" s="4"/>
-    </row>
-    <row r="32" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K32" s="4"/>
-    </row>
-    <row r="33" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K33" s="4"/>
-    </row>
-    <row r="34" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K34" s="4"/>
-    </row>
-    <row r="35" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K35" s="4"/>
-    </row>
-    <row r="36" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K36" s="4"/>
-    </row>
-    <row r="37" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K37" s="4"/>
-    </row>
-    <row r="38" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K38" s="4"/>
-    </row>
-    <row r="39" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K39" s="4"/>
-    </row>
-    <row r="40" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K40" s="4"/>
-    </row>
-    <row r="41" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K41" s="4"/>
-    </row>
-    <row r="42" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K42" s="4"/>
-    </row>
-    <row r="43" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K43" s="4"/>
-    </row>
-    <row r="44" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K44" s="4"/>
-    </row>
-    <row r="45" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K45" s="4"/>
-    </row>
-    <row r="46" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K46" s="4"/>
-    </row>
-    <row r="47" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K47" s="4"/>
-    </row>
-    <row r="48" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K48" s="4"/>
-    </row>
-    <row r="49" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K49" s="4"/>
-    </row>
-    <row r="50" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K50" s="4"/>
-    </row>
-    <row r="51" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K51" s="4"/>
-    </row>
-    <row r="52" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K52" s="4"/>
-    </row>
-    <row r="53" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K53" s="4"/>
-    </row>
-    <row r="54" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K54" s="4"/>
-    </row>
-    <row r="55" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K55" s="4"/>
-    </row>
-    <row r="56" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K56" s="4"/>
-    </row>
-    <row r="57" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K57" s="4"/>
-    </row>
-    <row r="58" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K58" s="4"/>
-    </row>
-    <row r="59" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K59" s="4"/>
-    </row>
-    <row r="60" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K60" s="4"/>
-    </row>
-    <row r="61" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K61" s="4"/>
-    </row>
-    <row r="62" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K62" s="4"/>
-    </row>
-    <row r="63" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K63" s="4"/>
-    </row>
-    <row r="64" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K64" s="4"/>
-    </row>
-    <row r="65" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K65" s="4"/>
-    </row>
-    <row r="66" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K66" s="4"/>
-    </row>
-    <row r="67" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K67" s="4"/>
-    </row>
-    <row r="68" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K68" s="4"/>
-    </row>
-    <row r="69" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K69" s="4"/>
-    </row>
-    <row r="70" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K70" s="4"/>
-    </row>
-    <row r="71" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K71" s="4"/>
-    </row>
-    <row r="72" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K72" s="4"/>
-    </row>
-    <row r="73" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K73" s="4"/>
-    </row>
-    <row r="74" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K74" s="4"/>
-    </row>
-    <row r="75" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K75" s="4"/>
-    </row>
-    <row r="76" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K76" s="4"/>
-    </row>
-    <row r="77" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K77" s="4"/>
-    </row>
-    <row r="78" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K78" s="4"/>
-    </row>
-    <row r="79" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K79" s="4"/>
-    </row>
-    <row r="80" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K80" s="4"/>
-    </row>
-    <row r="81" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K81" s="4"/>
-    </row>
-    <row r="82" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K82" s="4"/>
-    </row>
-    <row r="83" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K83" s="4"/>
-    </row>
-    <row r="84" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K84" s="4"/>
-    </row>
-    <row r="85" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K85" s="4"/>
-    </row>
-    <row r="86" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K86" s="4"/>
-    </row>
-    <row r="87" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K87" s="4"/>
-    </row>
-    <row r="88" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K88" s="4"/>
-    </row>
-    <row r="89" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K89" s="4"/>
-    </row>
-    <row r="90" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K90" s="4"/>
-    </row>
-    <row r="91" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K91" s="4"/>
-    </row>
-    <row r="92" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K92" s="4"/>
-    </row>
-    <row r="93" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K93" s="4"/>
-    </row>
-    <row r="94" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K94" s="4"/>
-    </row>
-    <row r="95" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K95" s="4"/>
-    </row>
-    <row r="96" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K96" s="4"/>
-    </row>
-    <row r="97" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K97" s="4"/>
-    </row>
-    <row r="98" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K98" s="4"/>
-    </row>
-    <row r="99" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K99" s="4"/>
-    </row>
-    <row r="100" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K100" s="4"/>
+      <c r="D4" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D53" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D56" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D62" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D64" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D65" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D66" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D67" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D68" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D69" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D70" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D71" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D72" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D73" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D74" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D75" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D76" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D77" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D78" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D79" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D80" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D81" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D83" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D84" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D85" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D86" s="2">
+        <v>391230913</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F100" xr:uid="{4D32BBE0-47EB-4052-9C13-CAD156617AC9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F85" xr:uid="{4D32BBE0-47EB-4052-9C13-CAD156617AC9}">
       <formula1>"Nhân viên kinh doanh tự tìm kiếm,Khách hàng hoặc đối tác giới thiệu,Thông qua sự kiện hội thảo tập huấn,Khách hàng tự tìm đến,Marketing,Khác"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G100" xr:uid="{6217FFF0-1943-4653-832C-AD469DDF876C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{6217FFF0-1943-4653-832C-AD469DDF876C}">
       <formula1>"Khách hàng bán lẻ,Khách hàng doanh nghiệp"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H100" xr:uid="{830D9541-9704-49E3-84FE-A54926A2CA82}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{830D9541-9704-49E3-84FE-A54926A2CA82}">
       <formula1>"Thương mại"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I100" xr:uid="{E4EE7E7B-BE2F-475B-8863-A35DBA405826}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{E4EE7E7B-BE2F-475B-8863-A35DBA405826}">
       <formula1>"Kinh doanh thực phẩm , kinh doanh hóa mĩ phẩm ,Kinh doanh điện tử điện lạnh, kinh doanh đồ gỗ, Kinh doanh hàng gia dụng , kinh doanh nông sản,Kinh doanh sắt thép , kinh doanh thương mại khác"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2" xr:uid="{0869C82E-FE33-4E08-BB8A-9FEBB18F4208}">
       <formula1>"Dưới 1 tỉ đồng , 1 tỉ đồng đến 3 tỉ đồng ,Từ 3 đến 5 tỉ đồng ,Trên 5 tỉ đồng"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P100" xr:uid="{AB5594FA-297D-4A82-8BD1-672AF30D7E71}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2" xr:uid="{AB5594FA-297D-4A82-8BD1-672AF30D7E71}">
       <formula1>"0 , 1"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2" xr:uid="{0953E154-6A45-4CAD-9873-0AD892E1F145}">
       <formula1>"0 ,1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R101" xr:uid="{4BC7B3C6-05D8-4782-A120-1652E5E2BEBC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2" xr:uid="{4BC7B3C6-05D8-4782-A120-1652E5E2BEBC}">
       <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{6F802F46-C0BD-42C2-B7A5-EBA638A6EB6C}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{FC082895-9FCE-4937-AADE-0553C48FBCCF}"/>
+    <hyperlink ref="E3:E86" r:id="rId2" display="test@345" xr:uid="{EEEA42D2-B310-4431-9E3B-F5F2649ACCC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>